--- a/src/data/downloads/2017_elections_of_municipal_authorities_runoff_20171021_data_2026-04-26T12-41-30.xlsx
+++ b/src/data/downloads/2017_elections_of_municipal_authorities_runoff_20171021_data_2026-04-26T12-41-30.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="59">
   <si>
     <t>district_id</t>
   </si>
@@ -123,13 +123,13 @@
     <t>Archive</t>
   </si>
   <si>
-    <t>Comprehensive Election Data Archive of Georgia (CEDAG)</t>
+    <t>Georgia Election Data Archive (GEDA)</t>
   </si>
   <si>
     <t>Website</t>
   </si>
   <si>
-    <t>https://electionsdata.ge</t>
+    <t>https://electionsdata.ge/elections?type=local&amp;election=local_2017&amp;sub=local_2017_r2</t>
   </si>
   <si>
     <t>Author</t>
@@ -141,25 +141,19 @@
     <t>Election (EN)</t>
   </si>
   <si>
-    <t>2017 elections of municipal authorities — Second Round</t>
+    <t>2017 elections of municipal authorities - Second Round</t>
   </si>
   <si>
     <t>Election (KA)</t>
   </si>
   <si>
-    <t>მუნიციპალიტეტის ორგანოთა 2017 წლის არჩევნები — მეორე ტური</t>
+    <t>მუნიციპალიტეტის ორგანოთა 2017 წლის არჩევნები - კენჭისყრის მეორე ტური</t>
   </si>
   <si>
     <t>Election ID</t>
   </si>
   <si>
     <t>local_2017</t>
-  </si>
-  <si>
-    <t>Sub-election ID</t>
-  </si>
-  <si>
-    <t>local_2017_r2</t>
   </si>
   <si>
     <t>Election Type</t>
@@ -177,7 +171,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-04-26T12:41:30.730Z</t>
+    <t>2026-04-30T18:50:28.616Z</t>
   </si>
   <si>
     <t>Data Source</t>
@@ -189,13 +183,13 @@
     <t>Citation (APA)</t>
   </si>
   <si>
-    <t>Sichinava, D. (2026). Results of the 2017 elections of municipal authorities — Second Round. Comprehensive Election Data Archive of Georgia (CEDAG). https://electionsdata.ge/local_2017</t>
+    <t>Sichinava, D. (2026). Results of the 2017 elections of municipal authorities - Second Round. Georgia Election Data Archive (GEDA). https://electionsdata.ge/elections?type=local&amp;election=local_2017&amp;sub=local_2017_r2</t>
   </si>
   <si>
     <t>License</t>
   </si>
   <si>
-    <t>Open data. Please cite CEDAG when using.</t>
+    <t>CC-BY-4.0</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1526,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -29409,13 +29403,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -29518,14 +29512,6 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
